--- a/AtchisonRegime/Outputs/Canada/df_regZScores_Canada.xlsx
+++ b/AtchisonRegime/Outputs/Canada/df_regZScores_Canada.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,7 +6062,7 @@
         <v>-1.15907664912445</v>
       </c>
       <c r="C331" t="n">
-        <v>0.09458390577924577</v>
+        <v>0.09177840895191415</v>
       </c>
       <c r="D331" t="n">
         <v>0.6607631425232638</v>
@@ -6079,7 +6079,7 @@
         <v>-1.189286116851168</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1116244582638488</v>
+        <v>0.1104426686636601</v>
       </c>
       <c r="D332" t="n">
         <v>0.6738196246178002</v>
@@ -6096,7 +6096,7 @@
         <v>-1.178902114643448</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1308996091349146</v>
+        <v>0.1301523842624262</v>
       </c>
       <c r="D333" t="n">
         <v>0.64392862120351</v>
@@ -6113,7 +6113,7 @@
         <v>-1.278628121662478</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1527007472235339</v>
+        <v>0.1503419548343929</v>
       </c>
       <c r="D334" t="n">
         <v>0.5453937035152667</v>
@@ -6130,7 +6130,7 @@
         <v>-1.374494603709673</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1721220892219018</v>
+        <v>0.16800720720337</v>
       </c>
       <c r="D335" t="n">
         <v>0.4012988812070913</v>
@@ -6147,7 +6147,7 @@
         <v>-1.390151577988231</v>
       </c>
       <c r="C336" t="n">
-        <v>0.1772707817448261</v>
+        <v>0.1732999046664966</v>
       </c>
       <c r="D336" t="n">
         <v>0.2692656463854147</v>
@@ -6164,7 +6164,7 @@
         <v>-1.325191021733015</v>
       </c>
       <c r="C337" t="n">
-        <v>0.1710330385060329</v>
+        <v>0.1587151530727753</v>
       </c>
       <c r="D337" t="n">
         <v>0.2201519689621168</v>
@@ -6181,7 +6181,7 @@
         <v>-1.221578075441744</v>
       </c>
       <c r="C338" t="n">
-        <v>0.150486126309403</v>
+        <v>0.1273918536019111</v>
       </c>
       <c r="D338" t="n">
         <v>0.1470370271165108</v>
@@ -6198,7 +6198,7 @@
         <v>-1.1752475478079</v>
       </c>
       <c r="C339" t="n">
-        <v>0.1191287375318849</v>
+        <v>0.08939277802379972</v>
       </c>
       <c r="D339" t="n">
         <v>0.1763511896644202</v>
@@ -6215,7 +6215,7 @@
         <v>-1.009799539259991</v>
       </c>
       <c r="C340" t="n">
-        <v>0.07483996014503268</v>
+        <v>0.04324614692355425</v>
       </c>
       <c r="D340" t="n">
         <v>0.1371594861448566</v>
@@ -6229,16 +6229,33 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.8349609292392597</v>
+        <v>-0.8803880031974337</v>
       </c>
       <c r="C341" t="n">
-        <v>0.05546106636326892</v>
+        <v>0.01723553256778737</v>
       </c>
       <c r="D341" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.762874187646539</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.01728298383277108</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
